--- a/Compititor's_Price/IKO_Prices/IKO_Prices_07-08-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_07-08-2026.xlsx
@@ -533,37 +533,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
-  (Session info: chrome=150.0.7871.189)
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff632240d25+155a5]
-	chromedriver!GetHandleVerifier [0x7ff632240d80+15600]
-	chromedriver!(No symbol) [0x7ff631d9594d]
-	chromedriver!(No symbol) [0x7ff631d92709]
-	chromedriver!(No symbol) [0x7ff631d82a91]
-	chromedriver!(No symbol) [0x7ff631d848ff]
-	chromedriver!(No symbol) [0x7ff631d83033]
-	chromedriver!(No symbol) [0x7ff631d827fb]
-	chromedriver!(No symbol) [0x7ff631d824b1]
-	chromedriver!(No symbol) [0x7ff631d80167]
-	chromedriver!(No symbol) [0x7ff631d808e2]
-	chromedriver!(No symbol) [0x7ff631d99bf6]
-	chromedriver!(No symbol) [0x7ff631e3ee24]
-	chromedriver!(No symbol) [0x7ff631e191ca]
-	chromedriver!(No symbol) [0x7ff631e3e01b]
-	chromedriver!(No symbol) [0x7ff631de2e6c]
-	chromedriver!(No symbol) [0x7ff631de3d93]
-	chromedriver!GetHandleVerifier [0x7ff632826431+5facb1]
-	chromedriver!GetHandleVerifier [0x7ff632820a9b+5f531b]
-	chromedriver!GetHandleVerifier [0x7ff632845865+61a0e5]
-	chromedriver!GetHandleVerifier [0x7ff63225dace+3234e]
-	chromedriver!GetHandleVerifier [0x7ff63226661c+3ae9c]
-	chromedriver!GetHandleVerifier [0x7ff63224ab74+1f3f4]
-	chromedriver!GetHandleVerifier [0x7ff63224ad04+1f584]
-	chromedriver!GetHandleVerifier [0x7ff63222d9d7+2257]
-	KERNEL32!BaseThreadInitThunk [0x7ffef13be957+17]
-	ntdll!RtlUserThreadStart [0x7ffef35aad6c+2c]
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
